--- a/ASTquizApp/qBanks/DWDM.xlsx
+++ b/ASTquizApp/qBanks/DWDM.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFBBFD4-C253-4A35-9A3B-4CB2C3B5F70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$137</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="516">
   <si>
     <t>Introduction</t>
   </si>
@@ -31,9 +30,6 @@
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>System</t>
   </si>
   <si>
     <t>C</t>
@@ -1590,12 +1586,6 @@
     <t>DOD</t>
   </si>
   <si>
-    <t>NO_Options</t>
-  </si>
-  <si>
-    <t>Question_Type</t>
-  </si>
-  <si>
     <t>DENCE WAVE DIVISION MULTIPLEXING</t>
   </si>
   <si>
@@ -1614,8 +1604,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1978,13 +1968,21 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2022,7 +2020,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2056,6 +2054,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2090,9 +2089,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2265,9 +2265,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O137"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M137"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" customWidth="1"/>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
@@ -2279,124 +2279,112 @@
     <col min="13" max="13" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="40" customFormat="1" ht="18.75">
+    <row r="1" spans="1:13" s="40" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="C1" s="39" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="E1" s="39" t="s">
         <v>510</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="F1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="39" t="s">
-        <v>511</v>
-      </c>
-      <c r="F1" s="39" t="s">
+      <c r="G1" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="H1" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="I1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="J1" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="K1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="L1" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="M1" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="39" t="s">
+    </row>
+    <row r="2" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="39" t="s">
-        <v>512</v>
-      </c>
-      <c r="O1" s="39" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="3" customFormat="1" ht="60">
-      <c r="A2" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1">
-        <v>2</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="22" t="s">
+      <c r="K2" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>511</v>
+      </c>
+      <c r="C3" s="41">
+        <v>2</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="41">
+        <v>2</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="1">
-        <v>4</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" ht="60">
-      <c r="A3" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>514</v>
-      </c>
-      <c r="C3" s="41">
-        <v>2</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="41">
-        <v>2</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>22</v>
       </c>
       <c r="I3" s="41" t="b">
         <v>1</v>
@@ -2409,37 +2397,31 @@
       <c r="M3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="41">
-        <v>2</v>
-      </c>
-      <c r="O3" s="41" t="s">
+    </row>
+    <row r="4" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" s="3" customFormat="1" ht="60">
-      <c r="A4" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="1" t="b">
         <v>1</v>
@@ -2452,19 +2434,13 @@
       <c r="M4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="1">
-        <v>2</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" s="3" customFormat="1" ht="60">
+    </row>
+    <row r="5" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -2473,45 +2449,39 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="1">
-        <v>4</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="3" customFormat="1" ht="60">
+    </row>
+    <row r="6" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
@@ -2529,36 +2499,30 @@
         <v>2</v>
       </c>
       <c r="H6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="M6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N6" s="1">
-        <v>4</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" ht="60">
+    </row>
+    <row r="7" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -2567,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -2576,36 +2540,30 @@
         <v>2</v>
       </c>
       <c r="H7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="J7" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="M7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N7" s="1">
-        <v>4</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" ht="60">
+    </row>
+    <row r="8" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -2623,36 +2581,30 @@
         <v>2</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="M8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N8" s="1">
         <v>4</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="60">
+    </row>
+    <row r="9" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -2661,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1">
         <v>2</v>
@@ -2670,36 +2622,30 @@
         <v>2</v>
       </c>
       <c r="H9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="K9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="M9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="1">
-        <v>4</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="60">
+    </row>
+    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -2717,36 +2663,30 @@
         <v>2</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J10" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="K10" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="L10" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="L10" s="18" t="s">
-        <v>182</v>
-      </c>
       <c r="M10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N10" s="1">
-        <v>4</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="60">
+    </row>
+    <row r="11" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -2755,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -2764,36 +2704,30 @@
         <v>2</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="L11" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="J11" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>185</v>
-      </c>
       <c r="M11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N11" s="1">
         <v>4</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="60">
+    </row>
+    <row r="12" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C12" s="1">
         <v>11</v>
@@ -2811,36 +2745,30 @@
         <v>2</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="J12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="K12" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J12" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="L12" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="1">
-        <v>4</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="60">
+    </row>
+    <row r="13" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C13" s="1">
         <v>12</v>
@@ -2849,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1">
         <v>2</v>
@@ -2858,36 +2786,30 @@
         <v>2</v>
       </c>
       <c r="H13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="19" t="s">
-        <v>40</v>
-      </c>
       <c r="J13" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="K13" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="L13" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="L13" s="19" t="s">
-        <v>190</v>
-      </c>
       <c r="M13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N13" s="1">
-        <v>4</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="60">
+    </row>
+    <row r="14" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C14" s="1">
         <v>13</v>
@@ -2905,36 +2827,30 @@
         <v>2</v>
       </c>
       <c r="H14" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="M14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N14" s="1">
-        <v>4</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C15" s="1">
         <v>14</v>
@@ -2952,36 +2868,30 @@
         <v>2</v>
       </c>
       <c r="H15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="L15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="1">
         <v>4</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="60">
+    </row>
+    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C16" s="1">
         <v>15</v>
@@ -2990,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1">
         <v>2</v>
@@ -2999,36 +2909,30 @@
         <v>2</v>
       </c>
       <c r="H16" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="I16" s="20" t="s">
-        <v>46</v>
-      </c>
       <c r="J16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="M16" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N16" s="1">
-        <v>4</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="60">
+    </row>
+    <row r="17" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C17" s="1">
         <v>16</v>
@@ -3037,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1">
         <v>2</v>
@@ -3046,36 +2950,30 @@
         <v>2</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="1">
-        <v>4</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="60">
+    </row>
+    <row r="18" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C18" s="1">
         <v>17</v>
@@ -3090,10 +2988,10 @@
         <v>2</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I18" s="20" t="b">
         <v>1</v>
@@ -3106,19 +3004,13 @@
       <c r="M18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="1">
-        <v>2</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="60">
+    </row>
+    <row r="19" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C19" s="1">
         <v>18</v>
@@ -3136,36 +3028,30 @@
         <v>2</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N19" s="1">
-        <v>4</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C20" s="1">
         <v>19</v>
@@ -3174,16 +3060,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1">
         <v>2</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I20" s="20" t="b">
         <v>1</v>
@@ -3196,19 +3082,13 @@
       <c r="M20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N20" s="1">
-        <v>2</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="60">
+    </row>
+    <row r="21" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C21" s="1">
         <v>20</v>
@@ -3217,16 +3097,16 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="1">
-        <v>2</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="H21" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I21" s="21" t="b">
         <v>1</v>
@@ -3239,19 +3119,13 @@
       <c r="M21" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="1">
-        <v>2</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="60">
+    </row>
+    <row r="22" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C22" s="1">
         <v>21</v>
@@ -3269,36 +3143,30 @@
         <v>2</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I22" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="J22" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="J22" s="29" t="s">
-        <v>203</v>
-      </c>
       <c r="K22" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="1">
         <v>4</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="60">
+    </row>
+    <row r="23" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C23" s="1">
         <v>22</v>
@@ -3316,36 +3184,30 @@
         <v>2</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="M23" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N23" s="1">
-        <v>4</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="60">
+    </row>
+    <row r="24" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C24" s="1">
         <v>23</v>
@@ -3354,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1">
         <v>2</v>
@@ -3363,36 +3225,30 @@
         <v>2</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I24" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J24" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="M24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="1">
-        <v>4</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="60">
+    </row>
+    <row r="25" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C25" s="1">
         <v>24</v>
@@ -3401,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
@@ -3410,36 +3266,30 @@
         <v>2</v>
       </c>
       <c r="H25" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N25" s="1">
-        <v>4</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C26" s="1">
         <v>25</v>
@@ -3457,36 +3307,30 @@
         <v>2</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I26" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="L26" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N26" s="1">
-        <v>4</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="60">
+    </row>
+    <row r="27" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C27" s="1">
         <v>26</v>
@@ -3504,36 +3348,30 @@
         <v>2</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="M27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="1">
         <v>4</v>
       </c>
-      <c r="O27" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="60">
+    </row>
+    <row r="28" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C28" s="1">
         <v>27</v>
@@ -3551,36 +3389,30 @@
         <v>2</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="M28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N28" s="1">
-        <v>4</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="60">
+    </row>
+    <row r="29" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -3589,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" s="1">
         <v>2</v>
@@ -3598,36 +3430,30 @@
         <v>2</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I29" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="K29" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N29" s="1">
-        <v>4</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="60">
+    </row>
+    <row r="30" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C30" s="1">
         <v>29</v>
@@ -3642,10 +3468,10 @@
         <v>2</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I30" s="20" t="b">
         <v>1</v>
@@ -3658,19 +3484,13 @@
       <c r="M30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N30" s="1">
-        <v>2</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="60">
+    </row>
+    <row r="31" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C31" s="1">
         <v>30</v>
@@ -3688,36 +3508,30 @@
         <v>2</v>
       </c>
       <c r="H31" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I31" s="20" t="s">
+      <c r="K31" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K31" s="7" t="s">
+      <c r="L31" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="M31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N31" s="1">
-        <v>4</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="60">
+    </row>
+    <row r="32" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C32" s="1">
         <v>31</v>
@@ -3726,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F32" s="1">
-        <v>2</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="H32" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I32" s="32" t="b">
         <v>1</v>
@@ -3748,19 +3562,13 @@
       <c r="M32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="1">
-        <v>4</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="60">
+    </row>
+    <row r="33" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C33" s="1">
         <v>32</v>
@@ -3769,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1">
         <v>2</v>
@@ -3778,36 +3586,30 @@
         <v>2</v>
       </c>
       <c r="H33" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="I33" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="I33" s="20" t="s">
-        <v>64</v>
-      </c>
       <c r="J33" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="M33" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N33" s="1">
-        <v>4</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="60">
+    </row>
+    <row r="34" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C34" s="1">
         <v>33</v>
@@ -3825,36 +3627,30 @@
         <v>2</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I34" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="L34" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N34" s="1">
-        <v>4</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C35" s="1">
         <v>34</v>
@@ -3872,36 +3668,30 @@
         <v>2</v>
       </c>
       <c r="H35" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="J35" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="L35" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="1">
-        <v>4</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="60">
+    </row>
+    <row r="36" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C36" s="1">
         <v>35</v>
@@ -3910,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" s="1">
         <v>2</v>
@@ -3919,36 +3709,30 @@
         <v>2</v>
       </c>
       <c r="H36" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="J36" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="I36" s="29" t="s">
+      <c r="K36" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="J36" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>238</v>
-      </c>
       <c r="L36" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N36" s="1">
-        <v>4</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="60">
+    </row>
+    <row r="37" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C37" s="1">
         <v>36</v>
@@ -3966,36 +3750,30 @@
         <v>2</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N37" s="1">
-        <v>4</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C38" s="1">
         <v>37</v>
@@ -4013,36 +3791,30 @@
         <v>2</v>
       </c>
       <c r="H38" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="I38" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="I38" s="20" t="s">
-        <v>70</v>
-      </c>
       <c r="J38" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="M38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N38" s="1">
-        <v>4</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="60">
+    </row>
+    <row r="39" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C39" s="1">
         <v>38</v>
@@ -4051,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1">
         <v>2</v>
@@ -4060,36 +3832,30 @@
         <v>2</v>
       </c>
       <c r="H39" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I39" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N39" s="1">
-        <v>4</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="60">
+    </row>
+    <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C40" s="1">
         <v>39</v>
@@ -4098,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" s="1">
         <v>2</v>
@@ -4107,36 +3873,30 @@
         <v>2</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I40" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="J40" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="J40" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" s="29" t="s">
+      <c r="L40" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="L40" s="29" t="s">
-        <v>246</v>
-      </c>
       <c r="M40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N40" s="1">
-        <v>4</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="60">
+    </row>
+    <row r="41" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C41" s="1">
         <v>40</v>
@@ -4154,36 +3914,30 @@
         <v>2</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J41" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N41" s="1">
-        <v>4</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="60">
+    </row>
+    <row r="42" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C42" s="1">
         <v>41</v>
@@ -4201,36 +3955,30 @@
         <v>2</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I42" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="K42" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="M42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N42" s="1">
         <v>4</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="60">
+    </row>
+    <row r="43" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C43" s="1">
         <v>42</v>
@@ -4239,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1">
         <v>2</v>
@@ -4248,36 +3996,30 @@
         <v>2</v>
       </c>
       <c r="H43" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I43" s="20" t="s">
+      <c r="K43" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="M43" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="1">
-        <v>4</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" s="9" customFormat="1" ht="60">
+    </row>
+    <row r="44" spans="1:13" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C44" s="1">
         <v>43</v>
@@ -4286,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1">
         <v>2</v>
@@ -4295,36 +4037,30 @@
         <v>2</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I44" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="J44" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="J44" s="19" t="s">
+      <c r="K44" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="K44" s="18" t="s">
+      <c r="L44" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="M44" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N44" s="1">
-        <v>4</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="60">
+    </row>
+    <row r="45" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C45" s="1">
         <v>44</v>
@@ -4339,10 +4075,10 @@
         <v>2</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I45" s="32" t="b">
         <v>1</v>
@@ -4355,19 +4091,13 @@
       <c r="M45" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="1">
-        <v>2</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="60">
+    </row>
+    <row r="46" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C46" s="1">
         <v>45</v>
@@ -4376,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F46" s="1">
         <v>2</v>
@@ -4385,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I46" s="33">
         <v>16</v>
@@ -4402,19 +4132,13 @@
       <c r="M46" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N46" s="1">
-        <v>4</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="60">
+    </row>
+    <row r="47" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C47" s="1">
         <v>46</v>
@@ -4432,36 +4156,30 @@
         <v>2</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I47" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="L47" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="K47" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="L47" s="19" t="s">
-        <v>259</v>
-      </c>
       <c r="M47" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N47" s="1">
-        <v>4</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C48" s="1">
         <v>47</v>
@@ -4479,36 +4197,30 @@
         <v>2</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="K48" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="M48" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N48" s="1">
         <v>4</v>
       </c>
-      <c r="O48" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="60">
+    </row>
+    <row r="49" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C49" s="1">
         <v>48</v>
@@ -4517,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1">
         <v>2</v>
@@ -4526,36 +4238,30 @@
         <v>2</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I49" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="J49" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="J49" s="20" t="s">
+      <c r="K49" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="K49" s="20" t="s">
+      <c r="L49" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="L49" s="20" t="s">
-        <v>267</v>
-      </c>
       <c r="M49" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N49" s="1">
-        <v>4</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="60">
+    </row>
+    <row r="50" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C50" s="1">
         <v>49</v>
@@ -4564,16 +4270,16 @@
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="1">
+        <v>2</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F50" s="1">
-        <v>2</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="H50" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I50" s="20" t="b">
         <v>1</v>
@@ -4586,19 +4292,13 @@
       <c r="M50" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N50" s="1">
-        <v>2</v>
-      </c>
-      <c r="O50" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="60">
+    </row>
+    <row r="51" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C51" s="1">
         <v>50</v>
@@ -4616,36 +4316,30 @@
         <v>2</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I51" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="J51" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="K51" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="J51" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="K51" s="19" t="s">
-        <v>269</v>
-      </c>
       <c r="L51" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N51" s="1">
-        <v>4</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="60">
+    </row>
+    <row r="52" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C52" s="1">
         <v>51</v>
@@ -4660,10 +4354,10 @@
         <v>2</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I52" s="32" t="b">
         <v>1</v>
@@ -4676,19 +4370,13 @@
       <c r="M52" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="1">
-        <v>2</v>
-      </c>
-      <c r="O52" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="60">
+    </row>
+    <row r="53" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C53" s="1">
         <v>52</v>
@@ -4697,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1">
         <v>2</v>
@@ -4706,36 +4394,30 @@
         <v>2</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I53" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="J53" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="J53" s="19" t="s">
-        <v>272</v>
-      </c>
       <c r="K53" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L53" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N53" s="1">
-        <v>4</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="60">
+    </row>
+    <row r="54" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C54" s="1">
         <v>53</v>
@@ -4744,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F54" s="1">
         <v>2</v>
@@ -4753,36 +4435,30 @@
         <v>2</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I54" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="J54" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="K54" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="J54" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="K54" s="19" t="s">
-        <v>276</v>
-      </c>
       <c r="L54" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="1">
-        <v>4</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="60">
+    </row>
+    <row r="55" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C55" s="1">
         <v>54</v>
@@ -4797,10 +4473,10 @@
         <v>2</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I55" s="32" t="b">
         <v>1</v>
@@ -4813,19 +4489,13 @@
       <c r="M55" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N55" s="1">
-        <v>2</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="60">
+    </row>
+    <row r="56" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C56" s="1">
         <v>55</v>
@@ -4834,45 +4504,39 @@
         <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F56" s="1">
+        <v>2</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H56" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="I56" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="J56" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="L56" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="M56" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F56" s="1">
-        <v>2</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H56" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="I56" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="J56" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="L56" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N56" s="1">
-        <v>4</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="60">
+    </row>
+    <row r="57" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C57" s="1">
         <v>56</v>
@@ -4881,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F57" s="1">
         <v>2</v>
@@ -4890,36 +4554,30 @@
         <v>2</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I57" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="J57" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="K57" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="J57" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="K57" s="19" t="s">
+      <c r="L57" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="L57" s="19" t="s">
-        <v>282</v>
-      </c>
       <c r="M57" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="1">
-        <v>4</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="60">
+    </row>
+    <row r="58" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C58" s="1">
         <v>57</v>
@@ -4937,7 +4595,7 @@
         <v>2</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I58" s="19">
         <v>16</v>
@@ -4954,19 +4612,13 @@
       <c r="M58" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N58" s="1">
-        <v>4</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="60">
+    </row>
+    <row r="59" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C59" s="1">
         <v>58</v>
@@ -4975,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1">
         <v>2</v>
@@ -4984,36 +4636,30 @@
         <v>2</v>
       </c>
       <c r="H59" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="J59" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="K59" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="I59" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="J59" s="19" t="s">
+      <c r="L59" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="K59" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="L59" s="19" t="s">
-        <v>285</v>
-      </c>
       <c r="M59" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="1">
         <v>4</v>
       </c>
-      <c r="O59" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="60">
+    </row>
+    <row r="60" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C60" s="1">
         <v>59</v>
@@ -5031,36 +4677,30 @@
         <v>2</v>
       </c>
       <c r="H60" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="J60" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="K60" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="I60" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="J60" s="19" t="s">
+      <c r="L60" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="K60" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="L60" s="19" t="s">
-        <v>288</v>
-      </c>
       <c r="M60" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N60" s="1">
         <v>4</v>
       </c>
-      <c r="O60" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="60">
+    </row>
+    <row r="61" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C61" s="1">
         <v>60</v>
@@ -5069,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F61" s="1">
         <v>2</v>
@@ -5078,36 +4718,30 @@
         <v>2</v>
       </c>
       <c r="H61" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="I61" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="J61" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="I61" s="19" t="s">
+      <c r="K61" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="J61" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="K61" s="33" t="s">
-        <v>290</v>
-      </c>
       <c r="L61" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M61" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N61" s="1">
-        <v>4</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="30.75" customHeight="1">
+    </row>
+    <row r="62" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C62" s="1">
         <v>61</v>
@@ -5125,7 +4759,7 @@
         <v>2</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I62" s="19">
         <v>1995</v>
@@ -5142,19 +4776,13 @@
       <c r="M62" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N62" s="1">
-        <v>4</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="34.5" customHeight="1">
+    </row>
+    <row r="63" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C63" s="1">
         <v>62</v>
@@ -5163,45 +4791,39 @@
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="1">
+        <v>2</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I63" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="J63" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="K63" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="L63" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="M63" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="1">
-        <v>2</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="I63" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="J63" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="K63" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="L63" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N63" s="1">
-        <v>4</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="60">
+    </row>
+    <row r="64" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C64" s="1">
         <v>63</v>
@@ -5219,36 +4841,30 @@
         <v>2</v>
       </c>
       <c r="H64" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="J64" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="I64" s="19" t="s">
+      <c r="K64" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="J64" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="K64" s="19" t="s">
+      <c r="L64" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="L64" s="19" t="s">
-        <v>295</v>
-      </c>
       <c r="M64" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N64" s="1">
-        <v>4</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="60">
+    </row>
+    <row r="65" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C65" s="1">
         <v>64</v>
@@ -5257,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1">
         <v>2</v>
@@ -5266,36 +4882,30 @@
         <v>2</v>
       </c>
       <c r="H65" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="I65" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="J65" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="I65" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="J65" s="19" t="s">
+      <c r="K65" s="19" t="s">
         <v>298</v>
       </c>
-      <c r="K65" s="19" t="s">
+      <c r="L65" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="L65" s="19" t="s">
-        <v>300</v>
-      </c>
       <c r="M65" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N65" s="1">
-        <v>4</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="60">
+    </row>
+    <row r="66" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C66" s="1">
         <v>65</v>
@@ -5304,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F66" s="1">
         <v>2</v>
@@ -5313,36 +4923,30 @@
         <v>2</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I66" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="J66" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="K66" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="J66" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="K66" s="19" t="s">
-        <v>302</v>
-      </c>
       <c r="L66" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N66" s="1">
         <v>4</v>
       </c>
-      <c r="O66" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="60">
+    </row>
+    <row r="67" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C67" s="1">
         <v>66</v>
@@ -5351,45 +4955,39 @@
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" s="1">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I67" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="J67" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="K67" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="L67" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="M67" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F67" s="1">
-        <v>2</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I67" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="J67" s="19" t="s">
-        <v>304</v>
-      </c>
-      <c r="K67" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="L67" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N67" s="1">
-        <v>4</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="35.25" customHeight="1">
+    </row>
+    <row r="68" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C68" s="1">
         <v>67</v>
@@ -5407,36 +5005,30 @@
         <v>2</v>
       </c>
       <c r="H68" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="I68" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="I68" s="19" t="s">
+      <c r="J68" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="K68" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="J68" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="K68" s="19" t="s">
-        <v>309</v>
-      </c>
       <c r="L68" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N68" s="1">
-        <v>4</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="29.25" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C69" s="1">
         <v>68</v>
@@ -5454,36 +5046,30 @@
         <v>2</v>
       </c>
       <c r="H69" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I69" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="I69" s="19" t="s">
-        <v>110</v>
-      </c>
       <c r="J69" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K69" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L69" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N69" s="1">
-        <v>4</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="60">
+    </row>
+    <row r="70" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C70" s="1">
         <v>69</v>
@@ -5492,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1">
         <v>2</v>
@@ -5501,36 +5087,30 @@
         <v>2</v>
       </c>
       <c r="H70" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I70" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="J70" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="K70" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="I70" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="J70" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="K70" s="19" t="s">
-        <v>112</v>
-      </c>
       <c r="L70" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N70" s="1">
         <v>4</v>
       </c>
-      <c r="O70" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" ht="60">
+    </row>
+    <row r="71" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C71" s="1">
         <v>70</v>
@@ -5539,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F71" s="1">
         <v>2</v>
@@ -5548,36 +5128,30 @@
         <v>2</v>
       </c>
       <c r="H71" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="I71" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="J71" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I71" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="J71" s="19" t="s">
-        <v>114</v>
-      </c>
       <c r="K71" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="L71" s="19" t="s">
         <v>310</v>
       </c>
-      <c r="L71" s="19" t="s">
-        <v>311</v>
-      </c>
       <c r="M71" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N71" s="1">
-        <v>4</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" ht="60">
+    </row>
+    <row r="72" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C72" s="1">
         <v>71</v>
@@ -5595,36 +5169,30 @@
         <v>2</v>
       </c>
       <c r="H72" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I72" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="J72" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="K72" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="I72" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="J72" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="K72" s="19" t="s">
-        <v>116</v>
-      </c>
       <c r="L72" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N72" s="1">
         <v>4</v>
       </c>
-      <c r="O72" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" ht="60">
+    </row>
+    <row r="73" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C73" s="1">
         <v>72</v>
@@ -5633,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1">
         <v>2</v>
@@ -5642,36 +5210,30 @@
         <v>2</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J73" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="K73" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="K73" s="19" t="s">
-        <v>310</v>
-      </c>
       <c r="L73" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N73" s="1">
-        <v>4</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" ht="60">
+    </row>
+    <row r="74" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C74" s="1">
         <v>73</v>
@@ -5689,36 +5251,30 @@
         <v>2</v>
       </c>
       <c r="H74" s="27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J74" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K74" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L74" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N74" s="1">
-        <v>4</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C75" s="1">
         <v>74</v>
@@ -5727,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1">
         <v>2</v>
@@ -5736,36 +5292,30 @@
         <v>2</v>
       </c>
       <c r="H75" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="I75" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="J75" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I75" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="J75" s="19" t="s">
-        <v>119</v>
-      </c>
       <c r="K75" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L75" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N75" s="1">
-        <v>4</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="60">
+    </row>
+    <row r="76" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C76" s="1">
         <v>75</v>
@@ -5783,36 +5333,30 @@
         <v>2</v>
       </c>
       <c r="H76" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I76" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="J76" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="K76" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="I76" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="J76" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="K76" s="19" t="s">
-        <v>121</v>
-      </c>
       <c r="L76" s="34" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N76" s="1">
         <v>4</v>
       </c>
-      <c r="O76" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" ht="60">
+    </row>
+    <row r="77" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C77" s="1">
         <v>76</v>
@@ -5830,36 +5374,30 @@
         <v>2</v>
       </c>
       <c r="H77" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I77" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="J77" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="I77" s="19" t="s">
+      <c r="K77" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="J77" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="K77" s="19" t="s">
-        <v>318</v>
-      </c>
       <c r="L77" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N77" s="1">
-        <v>4</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="60">
+    </row>
+    <row r="78" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C78" s="1">
         <v>77</v>
@@ -5868,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1">
         <v>2</v>
@@ -5877,36 +5415,30 @@
         <v>2</v>
       </c>
       <c r="H78" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="I78" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="I78" s="29" t="s">
-        <v>125</v>
-      </c>
       <c r="J78" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="K78" s="19" t="s">
         <v>319</v>
       </c>
-      <c r="K78" s="19" t="s">
-        <v>320</v>
-      </c>
       <c r="L78" s="34" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N78" s="1">
-        <v>4</v>
-      </c>
-      <c r="O78" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="60">
+    </row>
+    <row r="79" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C79" s="1">
         <v>78</v>
@@ -5915,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F79" s="1">
         <v>2</v>
@@ -5924,36 +5456,30 @@
         <v>2</v>
       </c>
       <c r="H79" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="I79" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J79" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="K79" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="L79" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="I79" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="J79" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="K79" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="L79" s="19" t="s">
-        <v>322</v>
-      </c>
       <c r="M79" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N79" s="1">
         <v>4</v>
       </c>
-      <c r="O79" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" ht="60">
+    </row>
+    <row r="80" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C80" s="1">
         <v>79</v>
@@ -5971,36 +5497,30 @@
         <v>2</v>
       </c>
       <c r="H80" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="I80" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="J80" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="I80" s="19" t="s">
+      <c r="K80" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="J80" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="K80" s="19" t="s">
+      <c r="L80" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="L80" s="19" t="s">
-        <v>327</v>
-      </c>
       <c r="M80" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="1">
-        <v>4</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" ht="60">
+    </row>
+    <row r="81" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C81" s="1">
         <v>80</v>
@@ -6015,10 +5535,10 @@
         <v>2</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I81" s="7" t="b">
         <v>1</v>
@@ -6031,19 +5551,13 @@
       <c r="M81" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="1">
-        <v>2</v>
-      </c>
-      <c r="O81" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" ht="60">
+    </row>
+    <row r="82" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C82" s="1">
         <v>81</v>
@@ -6052,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1">
         <v>2</v>
@@ -6061,36 +5575,30 @@
         <v>2</v>
       </c>
       <c r="H82" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I82" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="J82" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="I82" s="29" t="s">
+      <c r="K82" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="J82" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="K82" s="29" t="s">
+      <c r="L82" s="29" t="s">
         <v>330</v>
       </c>
-      <c r="L82" s="29" t="s">
-        <v>331</v>
-      </c>
       <c r="M82" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N82" s="1">
-        <v>4</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" ht="60">
+    </row>
+    <row r="83" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C83" s="1">
         <v>82</v>
@@ -6099,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F83" s="1">
         <v>2</v>
@@ -6108,36 +5616,30 @@
         <v>2</v>
       </c>
       <c r="H83" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="I83" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="J83" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="K83" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="L83" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="I83" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="J83" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="K83" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="L83" s="19" t="s">
-        <v>132</v>
-      </c>
       <c r="M83" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N83" s="1">
-        <v>4</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C84" s="1">
         <v>83</v>
@@ -6152,10 +5654,10 @@
         <v>2</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I84" s="7" t="b">
         <v>1</v>
@@ -6168,19 +5670,13 @@
       <c r="M84" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N84" s="1">
-        <v>2</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" ht="60">
+    </row>
+    <row r="85" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C85" s="1">
         <v>84</v>
@@ -6189,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1">
         <v>2</v>
@@ -6198,36 +5694,30 @@
         <v>2</v>
       </c>
       <c r="H85" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I85" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="J85" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I85" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="J85" s="19" t="s">
-        <v>135</v>
-      </c>
       <c r="K85" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M85" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N85" s="1">
-        <v>4</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" ht="60">
+    </row>
+    <row r="86" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C86" s="1">
         <v>85</v>
@@ -6245,36 +5735,30 @@
         <v>2</v>
       </c>
       <c r="H86" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N86" s="1">
-        <v>4</v>
-      </c>
-      <c r="O86" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C87" s="1">
         <v>86</v>
@@ -6292,36 +5776,30 @@
         <v>2</v>
       </c>
       <c r="H87" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="K87" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I87" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="K87" s="19" t="s">
-        <v>138</v>
-      </c>
       <c r="L87" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N87" s="1">
         <v>4</v>
       </c>
-      <c r="O87" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" ht="60">
+    </row>
+    <row r="88" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C88" s="1">
         <v>87</v>
@@ -6330,16 +5808,16 @@
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F88" s="1">
+        <v>2</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F88" s="1">
-        <v>2</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="H88" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I88" s="7" t="b">
         <v>1</v>
@@ -6352,19 +5830,13 @@
       <c r="M88" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N88" s="1">
-        <v>2</v>
-      </c>
-      <c r="O88" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" ht="60">
+    </row>
+    <row r="89" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C89" s="1">
         <v>88</v>
@@ -6373,45 +5845,39 @@
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="1">
+        <v>2</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="L89" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="M89" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="1">
-        <v>2</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="I89" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="L89" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="M89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N89" s="1">
-        <v>4</v>
-      </c>
-      <c r="O89" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" ht="60">
+    </row>
+    <row r="90" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C90" s="1">
         <v>89</v>
@@ -6429,36 +5895,30 @@
         <v>2</v>
       </c>
       <c r="H90" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="J90" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="I90" s="4" t="s">
+      <c r="K90" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="J90" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>341</v>
-      </c>
       <c r="L90" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N90" s="1">
-        <v>4</v>
-      </c>
-      <c r="O90" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" ht="60">
+    </row>
+    <row r="91" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C91" s="1">
         <v>90</v>
@@ -6467,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
@@ -6476,36 +5936,30 @@
         <v>2</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I91" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="J91" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="J91" s="4" t="s">
+      <c r="K91" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="K91" s="4" t="s">
-        <v>344</v>
-      </c>
       <c r="L91" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N91" s="1">
-        <v>4</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" ht="60">
+    </row>
+    <row r="92" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C92" s="1">
         <v>91</v>
@@ -6520,10 +5974,10 @@
         <v>2</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I92" s="7" t="b">
         <v>1</v>
@@ -6536,19 +5990,13 @@
       <c r="M92" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N92" s="1">
-        <v>2</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" ht="60">
+    </row>
+    <row r="93" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C93" s="1">
         <v>92</v>
@@ -6566,36 +6014,30 @@
         <v>2</v>
       </c>
       <c r="H93" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="J93" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="I93" s="4" t="s">
+      <c r="K93" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="J93" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="K93" s="4" t="s">
-        <v>346</v>
-      </c>
       <c r="L93" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N93" s="1">
-        <v>4</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" ht="60">
+    </row>
+    <row r="94" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C94" s="1">
         <v>93</v>
@@ -6604,45 +6046,39 @@
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="1">
+        <v>2</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="L94" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="M94" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F94" s="1">
-        <v>2</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="L94" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N94" s="1">
-        <v>4</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" ht="60">
+    </row>
+    <row r="95" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C95" s="1">
         <v>94</v>
@@ -6651,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F95" s="1">
         <v>2</v>
@@ -6660,36 +6096,30 @@
         <v>2</v>
       </c>
       <c r="H95" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I95" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="I95" s="19" t="s">
-        <v>151</v>
-      </c>
       <c r="J95" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K95" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="K95" s="4" t="s">
-        <v>351</v>
-      </c>
       <c r="L95" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N95" s="1">
-        <v>4</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" ht="60">
+    </row>
+    <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C96" s="1">
         <v>95</v>
@@ -6698,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1">
         <v>2</v>
@@ -6707,36 +6137,30 @@
         <v>2</v>
       </c>
       <c r="H96" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="K96" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="I96" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="K96" s="19" t="s">
-        <v>153</v>
-      </c>
       <c r="L96" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N96" s="1">
         <v>4</v>
       </c>
-      <c r="O96" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" ht="60">
+    </row>
+    <row r="97" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C97" s="1">
         <v>96</v>
@@ -6754,36 +6178,30 @@
         <v>2</v>
       </c>
       <c r="H97" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="J97" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="I97" s="4" t="s">
+      <c r="K97" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="J97" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="K97" s="4" t="s">
-        <v>355</v>
-      </c>
       <c r="L97" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M97" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N97" s="1">
-        <v>4</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" ht="60">
+    </row>
+    <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C98" s="1">
         <v>97</v>
@@ -6792,45 +6210,39 @@
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98" s="1">
+        <v>2</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="L98" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="M98" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F98" s="1">
-        <v>2</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="I98" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="L98" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="M98" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N98" s="1">
-        <v>4</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" ht="60">
+    </row>
+    <row r="99" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C99" s="1">
         <v>98</v>
@@ -6848,36 +6260,30 @@
         <v>2</v>
       </c>
       <c r="H99" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="I99" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="I99" s="19" t="s">
-        <v>159</v>
-      </c>
       <c r="J99" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="L99" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="K99" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>360</v>
-      </c>
       <c r="M99" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N99" s="1">
-        <v>4</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="60">
+    </row>
+    <row r="100" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C100" s="1">
         <v>99</v>
@@ -6886,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F100" s="1">
         <v>2</v>
@@ -6895,36 +6301,30 @@
         <v>2</v>
       </c>
       <c r="H100" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K100" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="I100" s="4" t="s">
+      <c r="L100" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="J100" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="K100" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>362</v>
-      </c>
       <c r="M100" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="1">
         <v>4</v>
       </c>
-      <c r="O100" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="60">
+    </row>
+    <row r="101" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C101" s="1">
         <v>100</v>
@@ -6933,45 +6333,39 @@
         <v>0</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="1">
+        <v>2</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H101" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="L101" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="M101" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F101" s="1">
-        <v>2</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H101" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="I101" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="J101" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="K101" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="L101" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="M101" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N101" s="1">
-        <v>4</v>
-      </c>
-      <c r="O101" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" ht="60">
+    </row>
+    <row r="102" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C102" s="1">
         <v>101</v>
@@ -6989,101 +6383,89 @@
         <v>2</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I102" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="J102" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="K102" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="J102" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="K102" s="4" t="s">
-        <v>355</v>
-      </c>
       <c r="L102" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M102" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="1">
-        <v>4</v>
-      </c>
-      <c r="O102" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="103" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C103" s="1">
         <v>102</v>
       </c>
       <c r="D103" s="35" t="s">
+        <v>373</v>
+      </c>
+      <c r="E103" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="35">
+        <v>2</v>
+      </c>
+      <c r="G103" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H103" s="36" t="s">
         <v>374</v>
       </c>
-      <c r="E103" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="F103" s="35">
-        <v>2</v>
-      </c>
-      <c r="G103" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H103" s="36" t="s">
+      <c r="I103" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="I103" s="35" t="s">
+      <c r="J103" s="35" t="s">
         <v>376</v>
       </c>
-      <c r="J103" s="35" t="s">
+      <c r="K103" s="35" t="s">
         <v>377</v>
       </c>
-      <c r="K103" s="35" t="s">
+      <c r="L103" s="35" t="s">
         <v>378</v>
       </c>
-      <c r="L103" s="35" t="s">
-        <v>379</v>
-      </c>
       <c r="M103" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N103" s="35">
-        <v>4</v>
-      </c>
-      <c r="O103" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="104" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C104" s="1">
         <v>103</v>
       </c>
       <c r="D104" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E104" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="F104" s="35">
+        <v>2</v>
+      </c>
+      <c r="G104" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F104" s="35">
-        <v>2</v>
-      </c>
-      <c r="G104" s="35" t="s">
-        <v>7</v>
-      </c>
       <c r="H104" s="36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I104" s="35" t="b">
         <v>1</v>
@@ -7096,25 +6478,19 @@
       <c r="M104" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N104" s="35">
-        <v>2</v>
-      </c>
-      <c r="O104" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="105" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C105" s="1">
         <v>104</v>
       </c>
       <c r="D105" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E105" s="35" t="s">
         <v>3</v>
@@ -7126,45 +6502,39 @@
         <v>2</v>
       </c>
       <c r="H105" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="I105" s="35" t="s">
+        <v>379</v>
+      </c>
+      <c r="J105" s="35" t="s">
         <v>382</v>
       </c>
-      <c r="I105" s="35" t="s">
-        <v>380</v>
-      </c>
-      <c r="J105" s="35" t="s">
+      <c r="K105" s="35" t="s">
         <v>383</v>
       </c>
-      <c r="K105" s="35" t="s">
+      <c r="L105" s="35" t="s">
         <v>384</v>
       </c>
-      <c r="L105" s="35" t="s">
-        <v>385</v>
-      </c>
       <c r="M105" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N105" s="35">
-        <v>4</v>
-      </c>
-      <c r="O105" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="106" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C106" s="1">
         <v>105</v>
       </c>
       <c r="D106" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E106" s="35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F106" s="35">
         <v>2</v>
@@ -7173,42 +6543,36 @@
         <v>2</v>
       </c>
       <c r="H106" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="I106" s="35" t="s">
         <v>386</v>
       </c>
-      <c r="I106" s="35" t="s">
+      <c r="J106" s="35" t="s">
         <v>387</v>
       </c>
-      <c r="J106" s="35" t="s">
+      <c r="K106" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="K106" s="35" t="s">
+      <c r="L106" s="35" t="s">
         <v>389</v>
       </c>
-      <c r="L106" s="35" t="s">
-        <v>390</v>
-      </c>
       <c r="M106" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="N106" s="35">
         <v>4</v>
       </c>
-      <c r="O106" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="107" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C107" s="1">
         <v>106</v>
       </c>
       <c r="D107" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E107" s="35" t="s">
         <v>1</v>
@@ -7220,42 +6584,36 @@
         <v>2</v>
       </c>
       <c r="H107" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="I107" s="35" t="s">
         <v>391</v>
       </c>
-      <c r="I107" s="35" t="s">
+      <c r="J107" s="35" t="s">
         <v>392</v>
       </c>
-      <c r="J107" s="35" t="s">
+      <c r="K107" s="35" t="s">
         <v>393</v>
       </c>
-      <c r="K107" s="35" t="s">
+      <c r="L107" s="35" t="s">
         <v>394</v>
       </c>
-      <c r="L107" s="35" t="s">
-        <v>395</v>
-      </c>
       <c r="M107" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N107" s="35">
-        <v>4</v>
-      </c>
-      <c r="O107" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C108" s="1">
         <v>107</v>
       </c>
       <c r="D108" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E108" s="35" t="s">
         <v>3</v>
@@ -7267,54 +6625,48 @@
         <v>2</v>
       </c>
       <c r="H108" s="36" t="s">
+        <v>395</v>
+      </c>
+      <c r="I108" s="35" t="s">
         <v>396</v>
       </c>
-      <c r="I108" s="35" t="s">
+      <c r="J108" s="35" t="s">
         <v>397</v>
       </c>
-      <c r="J108" s="35" t="s">
+      <c r="K108" s="35" t="s">
         <v>398</v>
       </c>
-      <c r="K108" s="35" t="s">
-        <v>399</v>
-      </c>
       <c r="L108" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M108" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N108" s="35">
-        <v>4</v>
-      </c>
-      <c r="O108" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C109" s="1">
         <v>108</v>
       </c>
       <c r="D109" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E109" s="35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F109" s="35">
         <v>2</v>
       </c>
       <c r="G109" s="35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H109" s="36" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I109" s="35" t="b">
         <v>1</v>
@@ -7327,37 +6679,31 @@
       <c r="M109" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N109" s="35">
-        <v>2</v>
-      </c>
-      <c r="O109" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="110" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C110" s="1">
         <v>109</v>
       </c>
       <c r="D110" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E110" s="35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F110" s="35">
         <v>2</v>
       </c>
       <c r="G110" s="35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H110" s="36" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I110" s="35" t="b">
         <v>1</v>
@@ -7370,37 +6716,31 @@
       <c r="M110" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N110" s="35">
-        <v>2</v>
-      </c>
-      <c r="O110" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="111" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C111" s="1">
         <v>110</v>
       </c>
       <c r="D111" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="E111" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F111" s="35">
+        <v>2</v>
+      </c>
+      <c r="G111" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="H111" s="36" t="s">
         <v>402</v>
-      </c>
-      <c r="E111" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="F111" s="35">
-        <v>2</v>
-      </c>
-      <c r="G111" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="H111" s="36" t="s">
-        <v>403</v>
       </c>
       <c r="I111" s="35" t="b">
         <v>1</v>
@@ -7413,25 +6753,19 @@
       <c r="M111" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N111" s="35">
-        <v>2</v>
-      </c>
-      <c r="O111" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="112" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C112" s="1">
         <v>111</v>
       </c>
       <c r="D112" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E112" s="35" t="s">
         <v>1</v>
@@ -7443,45 +6777,39 @@
         <v>2</v>
       </c>
       <c r="H112" s="36" t="s">
+        <v>403</v>
+      </c>
+      <c r="I112" s="35" t="s">
         <v>404</v>
       </c>
-      <c r="I112" s="35" t="s">
+      <c r="J112" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="J112" s="35" t="s">
+      <c r="K112" s="35" t="s">
         <v>406</v>
       </c>
-      <c r="K112" s="35" t="s">
+      <c r="L112" s="35" t="s">
         <v>407</v>
       </c>
-      <c r="L112" s="35" t="s">
-        <v>408</v>
-      </c>
       <c r="M112" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="N112" s="35">
         <v>4</v>
       </c>
-      <c r="O112" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="113" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C113" s="1">
         <v>112</v>
       </c>
       <c r="D113" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E113" s="35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F113" s="35">
         <v>2</v>
@@ -7490,42 +6818,36 @@
         <v>2</v>
       </c>
       <c r="H113" s="36" t="s">
+        <v>408</v>
+      </c>
+      <c r="I113" s="35" t="s">
         <v>409</v>
       </c>
-      <c r="I113" s="35" t="s">
+      <c r="J113" s="35" t="s">
         <v>410</v>
       </c>
-      <c r="J113" s="35" t="s">
+      <c r="K113" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="K113" s="35" t="s">
+      <c r="L113" s="35" t="s">
         <v>412</v>
       </c>
-      <c r="L113" s="35" t="s">
-        <v>413</v>
-      </c>
       <c r="M113" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N113" s="35">
-        <v>4</v>
-      </c>
-      <c r="O113" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C114" s="1">
         <v>113</v>
       </c>
       <c r="D114" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E114" s="35" t="s">
         <v>3</v>
@@ -7537,101 +6859,89 @@
         <v>2</v>
       </c>
       <c r="H114" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="I114" s="35" t="s">
         <v>414</v>
       </c>
-      <c r="I114" s="35" t="s">
+      <c r="J114" s="35" t="s">
         <v>415</v>
       </c>
-      <c r="J114" s="35" t="s">
+      <c r="K114" s="35" t="s">
         <v>416</v>
       </c>
-      <c r="K114" s="35" t="s">
-        <v>417</v>
-      </c>
       <c r="L114" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M114" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N114" s="35">
-        <v>4</v>
-      </c>
-      <c r="O114" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C115" s="1">
         <v>114</v>
       </c>
       <c r="D115" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E115" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F115" s="35">
+        <v>2</v>
+      </c>
+      <c r="G115" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H115" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="I115" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="J115" s="35" t="s">
+        <v>419</v>
+      </c>
+      <c r="K115" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="L115" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="M115" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="F115" s="35">
-        <v>2</v>
-      </c>
-      <c r="G115" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H115" s="36" t="s">
-        <v>418</v>
-      </c>
-      <c r="I115" s="35" t="s">
-        <v>419</v>
-      </c>
-      <c r="J115" s="35" t="s">
-        <v>420</v>
-      </c>
-      <c r="K115" s="35" t="s">
-        <v>421</v>
-      </c>
-      <c r="L115" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="M115" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N115" s="35">
-        <v>4</v>
-      </c>
-      <c r="O115" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="116" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C116" s="1">
         <v>115</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E116" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="F116" s="35">
+        <v>2</v>
+      </c>
+      <c r="G116" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F116" s="35">
-        <v>2</v>
-      </c>
-      <c r="G116" s="35" t="s">
-        <v>7</v>
-      </c>
       <c r="H116" s="36" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I116" s="35" t="b">
         <v>1</v>
@@ -7644,25 +6954,19 @@
       <c r="M116" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N116" s="35">
-        <v>2</v>
-      </c>
-      <c r="O116" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="117" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C117" s="1">
         <v>116</v>
       </c>
       <c r="D117" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E117" s="35" t="s">
         <v>1</v>
@@ -7674,101 +6978,89 @@
         <v>2</v>
       </c>
       <c r="H117" s="36" t="s">
+        <v>422</v>
+      </c>
+      <c r="I117" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="I117" s="35" t="s">
+      <c r="J117" s="35" t="s">
         <v>424</v>
       </c>
-      <c r="J117" s="35" t="s">
+      <c r="K117" s="35" t="s">
         <v>425</v>
       </c>
-      <c r="K117" s="35" t="s">
-        <v>426</v>
-      </c>
       <c r="L117" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M117" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N117" s="35">
-        <v>4</v>
-      </c>
-      <c r="O117" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C118" s="1">
         <v>117</v>
       </c>
       <c r="D118" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="E118" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F118" s="35">
+        <v>2</v>
+      </c>
+      <c r="G118" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H118" s="36" t="s">
         <v>427</v>
       </c>
-      <c r="E118" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="F118" s="35">
-        <v>2</v>
-      </c>
-      <c r="G118" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H118" s="36" t="s">
+      <c r="I118" s="35" t="s">
         <v>428</v>
       </c>
-      <c r="I118" s="35" t="s">
+      <c r="J118" s="35" t="s">
         <v>429</v>
       </c>
-      <c r="J118" s="35" t="s">
+      <c r="K118" s="35" t="s">
         <v>430</v>
       </c>
-      <c r="K118" s="35" t="s">
+      <c r="L118" s="35" t="s">
         <v>431</v>
       </c>
-      <c r="L118" s="35" t="s">
-        <v>432</v>
-      </c>
       <c r="M118" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N118" s="35">
-        <v>4</v>
-      </c>
-      <c r="O118" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="119" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C119" s="1">
         <v>118</v>
       </c>
       <c r="D119" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E119" s="35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F119" s="35">
         <v>2</v>
       </c>
       <c r="G119" s="35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H119" s="36" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I119" s="35" t="b">
         <v>1</v>
@@ -7781,28 +7073,22 @@
       <c r="M119" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N119" s="35">
-        <v>2</v>
-      </c>
-      <c r="O119" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="120" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C120" s="1">
         <v>119</v>
       </c>
       <c r="D120" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E120" s="35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F120" s="35">
         <v>2</v>
@@ -7811,42 +7097,36 @@
         <v>2</v>
       </c>
       <c r="H120" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I120" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="I120" s="35" t="s">
+      <c r="J120" s="35" t="s">
         <v>435</v>
       </c>
-      <c r="J120" s="35" t="s">
+      <c r="K120" s="35" t="s">
         <v>436</v>
       </c>
-      <c r="K120" s="35" t="s">
+      <c r="L120" s="35" t="s">
         <v>437</v>
       </c>
-      <c r="L120" s="35" t="s">
-        <v>438</v>
-      </c>
       <c r="M120" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N120" s="35">
-        <v>4</v>
-      </c>
-      <c r="O120" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="121" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C121" s="1">
         <v>120</v>
       </c>
       <c r="D121" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E121" s="35" t="s">
         <v>3</v>
@@ -7858,101 +7138,89 @@
         <v>2</v>
       </c>
       <c r="H121" s="36" t="s">
+        <v>438</v>
+      </c>
+      <c r="I121" s="35" t="s">
         <v>439</v>
       </c>
-      <c r="I121" s="35" t="s">
+      <c r="J121" s="35" t="s">
         <v>440</v>
       </c>
-      <c r="J121" s="35" t="s">
+      <c r="K121" s="35" t="s">
         <v>441</v>
       </c>
-      <c r="K121" s="35" t="s">
+      <c r="L121" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="L121" s="35" t="s">
-        <v>443</v>
-      </c>
       <c r="M121" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N121" s="35">
-        <v>4</v>
-      </c>
-      <c r="O121" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C122" s="1">
         <v>121</v>
       </c>
       <c r="D122" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E122" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F122" s="35">
+        <v>2</v>
+      </c>
+      <c r="G122" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H122" s="36" t="s">
+        <v>443</v>
+      </c>
+      <c r="I122" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="J122" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="K122" s="35" t="s">
+        <v>446</v>
+      </c>
+      <c r="L122" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="M122" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="F122" s="35">
-        <v>2</v>
-      </c>
-      <c r="G122" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H122" s="36" t="s">
-        <v>444</v>
-      </c>
-      <c r="I122" s="35" t="s">
-        <v>445</v>
-      </c>
-      <c r="J122" s="35" t="s">
-        <v>446</v>
-      </c>
-      <c r="K122" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="L122" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="M122" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N122" s="35">
-        <v>4</v>
-      </c>
-      <c r="O122" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="123" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C123" s="1">
         <v>122</v>
       </c>
       <c r="D123" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E123" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="F123" s="35">
+        <v>2</v>
+      </c>
+      <c r="G123" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F123" s="35">
-        <v>2</v>
-      </c>
-      <c r="G123" s="35" t="s">
-        <v>7</v>
-      </c>
       <c r="H123" s="38" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I123" s="35" t="b">
         <v>1</v>
@@ -7965,25 +7233,19 @@
       <c r="M123" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N123" s="35">
-        <v>2</v>
-      </c>
-      <c r="O123" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="124" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C124" s="1">
         <v>123</v>
       </c>
       <c r="D124" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E124" s="35" t="s">
         <v>1</v>
@@ -7992,10 +7254,10 @@
         <v>2</v>
       </c>
       <c r="G124" s="35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H124" s="36" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I124" s="35" t="b">
         <v>1</v>
@@ -8008,25 +7270,19 @@
       <c r="M124" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N124" s="35">
-        <v>2</v>
-      </c>
-      <c r="O124" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="125" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C125" s="1">
         <v>124</v>
       </c>
       <c r="D125" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E125" s="35" t="s">
         <v>3</v>
@@ -8038,183 +7294,159 @@
         <v>2</v>
       </c>
       <c r="H125" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="I125" s="35" t="s">
         <v>450</v>
       </c>
-      <c r="I125" s="35" t="s">
+      <c r="J125" s="35" t="s">
         <v>451</v>
       </c>
-      <c r="J125" s="35" t="s">
+      <c r="K125" s="35" t="s">
         <v>452</v>
       </c>
-      <c r="K125" s="35" t="s">
+      <c r="L125" s="35" t="s">
         <v>453</v>
       </c>
-      <c r="L125" s="35" t="s">
-        <v>454</v>
-      </c>
       <c r="M125" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N125" s="35">
-        <v>4</v>
-      </c>
-      <c r="O125" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C126" s="1">
         <v>125</v>
       </c>
       <c r="D126" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E126" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F126" s="35">
+        <v>2</v>
+      </c>
+      <c r="G126" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H126" s="36" t="s">
+        <v>454</v>
+      </c>
+      <c r="I126" s="35" t="s">
+        <v>450</v>
+      </c>
+      <c r="J126" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="K126" s="35" t="s">
+        <v>456</v>
+      </c>
+      <c r="L126" s="35" t="s">
+        <v>457</v>
+      </c>
+      <c r="M126" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="F126" s="35">
-        <v>2</v>
-      </c>
-      <c r="G126" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H126" s="36" t="s">
-        <v>455</v>
-      </c>
-      <c r="I126" s="35" t="s">
-        <v>451</v>
-      </c>
-      <c r="J126" s="35" t="s">
-        <v>456</v>
-      </c>
-      <c r="K126" s="35" t="s">
-        <v>457</v>
-      </c>
-      <c r="L126" s="35" t="s">
-        <v>458</v>
-      </c>
-      <c r="M126" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N126" s="35">
-        <v>4</v>
-      </c>
-      <c r="O126" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="127" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C127" s="1">
         <v>126</v>
       </c>
       <c r="D127" s="35" t="s">
+        <v>458</v>
+      </c>
+      <c r="E127" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="F127" s="35">
+        <v>2</v>
+      </c>
+      <c r="G127" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H127" s="36" t="s">
         <v>459</v>
       </c>
-      <c r="E127" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F127" s="35">
-        <v>2</v>
-      </c>
-      <c r="G127" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H127" s="36" t="s">
+      <c r="I127" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="I127" s="35" t="s">
+      <c r="J127" s="35" t="s">
         <v>461</v>
       </c>
-      <c r="J127" s="35" t="s">
+      <c r="K127" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="K127" s="35" t="s">
-        <v>463</v>
-      </c>
       <c r="L127" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M127" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N127" s="35">
-        <v>4</v>
-      </c>
-      <c r="O127" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C128" s="1">
         <v>127</v>
       </c>
       <c r="D128" s="35" t="s">
+        <v>463</v>
+      </c>
+      <c r="E128" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F128" s="35">
+        <v>2</v>
+      </c>
+      <c r="G128" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H128" s="36" t="s">
         <v>464</v>
       </c>
-      <c r="E128" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="F128" s="35">
-        <v>2</v>
-      </c>
-      <c r="G128" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H128" s="36" t="s">
+      <c r="I128" s="35" t="s">
         <v>465</v>
       </c>
-      <c r="I128" s="35" t="s">
+      <c r="J128" s="35" t="s">
         <v>466</v>
       </c>
-      <c r="J128" s="35" t="s">
+      <c r="K128" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="K128" s="35" t="s">
+      <c r="L128" s="35" t="s">
         <v>468</v>
       </c>
-      <c r="L128" s="35" t="s">
-        <v>469</v>
-      </c>
       <c r="M128" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="N128" s="35">
-        <v>4</v>
-      </c>
-      <c r="O128" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="129" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C129" s="1">
         <v>128</v>
       </c>
       <c r="D129" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E129" s="35" t="s">
         <v>1</v>
@@ -8226,42 +7458,36 @@
         <v>2</v>
       </c>
       <c r="H129" s="36" t="s">
+        <v>469</v>
+      </c>
+      <c r="I129" s="35" t="s">
         <v>470</v>
       </c>
-      <c r="I129" s="35" t="s">
+      <c r="J129" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="J129" s="35" t="s">
+      <c r="K129" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="K129" s="35" t="s">
+      <c r="L129" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="L129" s="35" t="s">
-        <v>474</v>
-      </c>
       <c r="M129" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="N129" s="35">
         <v>4</v>
       </c>
-      <c r="O129" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="130" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C130" s="1">
         <v>129</v>
       </c>
       <c r="D130" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E130" s="35" t="s">
         <v>3</v>
@@ -8273,233 +7499,203 @@
         <v>2</v>
       </c>
       <c r="H130" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="I130" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="I130" s="35" t="s">
+      <c r="J130" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="J130" s="35" t="s">
+      <c r="K130" s="35" t="s">
         <v>477</v>
       </c>
-      <c r="K130" s="35" t="s">
+      <c r="L130" s="35" t="s">
         <v>478</v>
       </c>
-      <c r="L130" s="35" t="s">
-        <v>479</v>
-      </c>
       <c r="M130" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="N130" s="35">
-        <v>4</v>
-      </c>
-      <c r="O130" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="131" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C131" s="1">
         <v>130</v>
       </c>
       <c r="D131" s="35" t="s">
+        <v>479</v>
+      </c>
+      <c r="E131" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="F131" s="35">
+        <v>2</v>
+      </c>
+      <c r="G131" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H131" s="36" t="s">
         <v>480</v>
       </c>
-      <c r="E131" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F131" s="35">
-        <v>2</v>
-      </c>
-      <c r="G131" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H131" s="36" t="s">
+      <c r="I131" s="35" t="s">
         <v>481</v>
       </c>
-      <c r="I131" s="35" t="s">
+      <c r="J131" s="35" t="s">
         <v>482</v>
       </c>
-      <c r="J131" s="35" t="s">
+      <c r="K131" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="K131" s="35" t="s">
+      <c r="L131" s="35" t="s">
         <v>484</v>
       </c>
-      <c r="L131" s="35" t="s">
-        <v>485</v>
-      </c>
       <c r="M131" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="N131" s="35">
         <v>4</v>
       </c>
-      <c r="O131" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="132" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C132" s="1">
         <v>131</v>
       </c>
       <c r="D132" s="35" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E132" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F132" s="35">
+        <v>2</v>
+      </c>
+      <c r="G132" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H132" s="36" t="s">
+        <v>485</v>
+      </c>
+      <c r="I132" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="J132" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="K132" s="35" t="s">
+        <v>488</v>
+      </c>
+      <c r="L132" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="M132" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="35">
-        <v>2</v>
-      </c>
-      <c r="G132" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H132" s="36" t="s">
-        <v>486</v>
-      </c>
-      <c r="I132" s="35" t="s">
-        <v>487</v>
-      </c>
-      <c r="J132" s="35" t="s">
-        <v>488</v>
-      </c>
-      <c r="K132" s="35" t="s">
-        <v>489</v>
-      </c>
-      <c r="L132" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="M132" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N132" s="35">
-        <v>4</v>
-      </c>
-      <c r="O132" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="133" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C133" s="1">
         <v>132</v>
       </c>
       <c r="D133" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="E133" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F133" s="35">
+        <v>2</v>
+      </c>
+      <c r="G133" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H133" s="36" t="s">
         <v>490</v>
       </c>
-      <c r="E133" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="F133" s="35">
-        <v>2</v>
-      </c>
-      <c r="G133" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H133" s="36" t="s">
+      <c r="I133" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="I133" s="35" t="s">
+      <c r="J133" s="35" t="s">
         <v>492</v>
       </c>
-      <c r="J133" s="35" t="s">
+      <c r="K133" s="35" t="s">
         <v>493</v>
       </c>
-      <c r="K133" s="35" t="s">
+      <c r="L133" s="35" t="s">
         <v>494</v>
       </c>
-      <c r="L133" s="35" t="s">
-        <v>495</v>
-      </c>
       <c r="M133" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="N133" s="35">
         <v>4</v>
       </c>
-      <c r="O133" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="134" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C134" s="1">
         <v>133</v>
       </c>
       <c r="D134" s="35" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E134" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F134" s="35">
+        <v>2</v>
+      </c>
+      <c r="G134" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H134" s="36" t="s">
+        <v>495</v>
+      </c>
+      <c r="I134" s="35" t="s">
+        <v>496</v>
+      </c>
+      <c r="J134" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="K134" s="35" t="s">
+        <v>498</v>
+      </c>
+      <c r="L134" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="M134" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="F134" s="35">
-        <v>2</v>
-      </c>
-      <c r="G134" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H134" s="36" t="s">
-        <v>496</v>
-      </c>
-      <c r="I134" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="J134" s="35" t="s">
-        <v>498</v>
-      </c>
-      <c r="K134" s="35" t="s">
-        <v>499</v>
-      </c>
-      <c r="L134" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="M134" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N134" s="35">
-        <v>4</v>
-      </c>
-      <c r="O134" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="135" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C135" s="1">
         <v>134</v>
       </c>
       <c r="D135" s="35" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E135" s="35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F135" s="35">
         <v>2</v>
@@ -8508,42 +7704,36 @@
         <v>2</v>
       </c>
       <c r="H135" s="36" t="s">
+        <v>499</v>
+      </c>
+      <c r="I135" s="35" t="s">
         <v>500</v>
       </c>
-      <c r="I135" s="35" t="s">
+      <c r="J135" s="35" t="s">
         <v>501</v>
       </c>
-      <c r="J135" s="35" t="s">
+      <c r="K135" s="35" t="s">
         <v>502</v>
       </c>
-      <c r="K135" s="35" t="s">
-        <v>503</v>
-      </c>
       <c r="L135" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M135" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="N135" s="35">
-        <v>4</v>
-      </c>
-      <c r="O135" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" s="37" customFormat="1" ht="60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C136" s="1">
         <v>135</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E136" s="35" t="s">
         <v>3</v>
@@ -8552,10 +7742,10 @@
         <v>2</v>
       </c>
       <c r="G136" s="35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H136" s="36" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I136" s="35" t="b">
         <v>1</v>
@@ -8568,25 +7758,19 @@
       <c r="M136" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N136" s="35">
-        <v>2</v>
-      </c>
-      <c r="O136" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" s="37" customFormat="1" ht="60">
+    </row>
+    <row r="137" spans="1:13" s="37" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C137" s="1">
         <v>136</v>
       </c>
       <c r="D137" s="35" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E137" s="35" t="s">
         <v>1</v>
@@ -8598,28 +7782,22 @@
         <v>2</v>
       </c>
       <c r="H137" s="36" t="s">
+        <v>504</v>
+      </c>
+      <c r="I137" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="I137" s="35" t="s">
+      <c r="J137" s="35" t="s">
         <v>506</v>
       </c>
-      <c r="J137" s="35" t="s">
+      <c r="K137" s="35" t="s">
         <v>507</v>
       </c>
-      <c r="K137" s="35" t="s">
+      <c r="L137" s="35" t="s">
         <v>508</v>
       </c>
-      <c r="L137" s="35" t="s">
-        <v>509</v>
-      </c>
       <c r="M137" s="35" t="s">
         <v>3</v>
-      </c>
-      <c r="N137" s="35">
-        <v>4</v>
-      </c>
-      <c r="O137" s="35" t="s">
-        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -8648,22 +7826,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>